--- a/Donnees/Statisiques Environnementales et de la  gouvernace/Environnement/Environment.xlsx
+++ b/Donnees/Statisiques Environnementales et de la  gouvernace/Environnement/Environment.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\Ansade_Project\Donnees\Statisiques Environnementales et de la  gouvernace\Environnement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{921B1046-B8CD-4A2E-A5C0-4B6ECCB89B2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1829BFC-4131-42BA-AFD9-0FE0AC38F47B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{547058C1-2FBA-45AB-89E5-8BEBC8B5FFB5}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{547058C1-2FBA-45AB-89E5-8BEBC8B5FFB5}"/>
   </bookViews>
   <sheets>
     <sheet name="T4.30" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="51">
   <si>
     <t xml:space="preserve">Hodh Chargui </t>
   </si>
@@ -144,15 +144,6 @@
     <t>Superficies (km²) ~2019</t>
   </si>
   <si>
-    <t>Source : Ministère de l’Environnement et du Développement durabl</t>
-  </si>
-  <si>
-    <t>Source :Ministère de l’Environnement et du Développement durabl</t>
-  </si>
-  <si>
-    <t>Source :EPCV 2004, 2008, 2014 et 2019</t>
-  </si>
-  <si>
     <t>Superficies (km²) ~2020</t>
   </si>
   <si>
@@ -168,22 +159,28 @@
     <t>Superficies (km²) ~2024</t>
   </si>
   <si>
-    <t>Tableau 4.33: L'évolution de la proportion(en %) des ménages qui ont adopté des énergies alternatives propres telles que le gaz butane dans leurs cuissons durant la période  2O04-2019</t>
-  </si>
-  <si>
     <t>Tiris-Zemmour</t>
   </si>
   <si>
-    <t>Source : Ministère de l’Environnement et du Développement durable</t>
-  </si>
-  <si>
-    <t>Tableau 4.32: Quantité  (en tonnes) de charbon transportée de l'intérieur vers Nouakchott  durant la période 2010-2019</t>
-  </si>
-  <si>
-    <t>Tableau 4.30 : Nombre annuel des incendies et feux de brousse enregistrés durant la période  2008-2024</t>
-  </si>
-  <si>
-    <t>Tableau 4.31: Superficies annuellement brulées par les incendies et feux de brousse durant la période 2008-2024</t>
+    <t>Tableau 3.1.1 : Nombre annuel des incendies et feux de brousse enregistrés durant la période  2008-2024</t>
+  </si>
+  <si>
+    <t>Tableau 3.1.2 : Superficies annuellement brulées par les incendies et feux de brousse durant la période 2008-2024</t>
+  </si>
+  <si>
+    <t>Tableau 3.1.3: Quantité  (en tonnes) de charbon transportée de l'intérieur vers Nouakchott  durant la période 2010-2019</t>
+  </si>
+  <si>
+    <t>Tableau 3.1.4: L'évolution de la proportion(en %) des ménages qui ont adopté des énergies alternatives propres telles que le gaz butane dans leurs cuissons durant la période  2004-2019</t>
+  </si>
+  <si>
+    <t>Source : MEDD/2008-2024</t>
+  </si>
+  <si>
+    <t>Source : EPCV/2004-2019</t>
+  </si>
+  <si>
+    <t>Source : MEDD/2010-2019</t>
   </si>
 </sst>
 </file>
@@ -755,7 +752,7 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1287,7 +1284,7 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="27" thickBot="1" x14ac:dyDescent="0.35">
@@ -1331,19 +1328,19 @@
         <v>37</v>
       </c>
       <c r="N2" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="O2" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="P2" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q2" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="O2" s="8" t="s">
+      <c r="R2" s="8" t="s">
         <v>42</v>
-      </c>
-      <c r="P2" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q2" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="R2" s="8" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1796,7 +1793,7 @@
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -1815,7 +1812,7 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -1890,7 +1887,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -1909,7 +1906,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B1" s="14"/>
       <c r="C1" s="14"/>
@@ -2105,7 +2102,7 @@
     </row>
     <row r="13" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A13" s="17" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B13" s="23">
         <v>71.703546653137593</v>
@@ -2173,7 +2170,7 @@
     </row>
     <row r="17" spans="1:1" ht="15" x14ac:dyDescent="0.3">
       <c r="A17" s="18" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="15.45" customHeight="1" x14ac:dyDescent="0.3"/>
